--- a/data/trans_orig/P1409-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1409-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de asma en 2012</t>
+          <t>Población con diagnóstico de asma en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2944</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13388</t>
+          <t>12928</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1123</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12620</t>
+          <t>13420</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>5987</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21149</t>
+          <t>20818</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>423823</t>
+          <t>424283</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>434267</t>
+          <t>434319</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>301834</t>
+          <t>301034</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313331</t>
+          <t>312571</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>730516</t>
+          <t>730847</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>745032</t>
+          <t>745678</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,2%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2087</t>
+          <t>2071</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15972</t>
+          <t>14165</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7610</t>
+          <t>7129</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23898</t>
+          <t>24203</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11747</t>
+          <t>12514</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31644</t>
+          <t>32047</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>402825</t>
+          <t>404632</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>416710</t>
+          <t>416726</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>314113</t>
+          <t>313808</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>330401</t>
+          <t>330882</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>725164</t>
+          <t>724761</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>745061</t>
+          <t>744294</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,35%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5985</t>
+          <t>5571</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19402</t>
+          <t>18466</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2985</t>
+          <t>3002</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14997</t>
+          <t>15204</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10992</t>
+          <t>11021</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29202</t>
+          <t>28723</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>610013</t>
+          <t>610949</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>623430</t>
+          <t>623844</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>245132</t>
+          <t>244925</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>257144</t>
+          <t>257127</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>860342</t>
+          <t>860821</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>878552</t>
+          <t>878523</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15524</t>
+          <t>14874</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34526</t>
+          <t>35280</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12532</t>
+          <t>12635</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29841</t>
+          <t>31931</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31744</t>
+          <t>31291</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>58020</t>
+          <t>57464</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1124483</t>
+          <t>1123729</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1143485</t>
+          <t>1144135</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>734881</t>
+          <t>732791</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>752190</t>
+          <t>752087</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1865711</t>
+          <t>1866267</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1891987</t>
+          <t>1892440</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,37%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6052</t>
+          <t>5858</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20292</t>
+          <t>20373</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15330</t>
+          <t>14796</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35337</t>
+          <t>34798</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23772</t>
+          <t>24207</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>47657</t>
+          <t>47432</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>490304</t>
+          <t>490223</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>504544</t>
+          <t>504738</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>724909</t>
+          <t>725448</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>744916</t>
+          <t>745450</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1223186</t>
+          <t>1223411</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1247071</t>
+          <t>1246636</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2793</t>
+          <t>2909</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13507</t>
+          <t>13384</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17735</t>
+          <t>17569</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>38294</t>
+          <t>37552</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,47 +2497,47 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
+          <t>3,39%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>33666</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>23787</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>47596</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
           <t>3,46%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>33666</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>23290</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>46081</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>253375</t>
+          <t>253498</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>264089</t>
+          <t>263973</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1069875</t>
+          <t>1070617</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1090434</t>
+          <t>1090600</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,47 +2610,47 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
+          <t>96,61%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>98,41%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>1275</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>1341385</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>1327455</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>1351264</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>97,55%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
           <t>96,54%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>98,4%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1275</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>1341385</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>1328970</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>1351761</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>97,55%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>96,65%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>51009</t>
+          <t>50078</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>84901</t>
+          <t>83475</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>77546</t>
+          <t>76722</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>117115</t>
+          <t>119016</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>136321</t>
+          <t>140092</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>191124</t>
+          <t>190117</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3337009</t>
+          <t>3338435</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3370901</t>
+          <t>3371832</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3428617</t>
+          <t>3426716</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3468186</t>
+          <t>3469010</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6776518</t>
+          <t>6777525</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6831321</t>
+          <t>6827550</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,99%</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de asma en 2016</t>
+          <t>Población con diagnóstico de asma en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3389</t>
+          <t>3795</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15603</t>
+          <t>16285</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4853</t>
+          <t>4984</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17384</t>
+          <t>17027</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10591</t>
+          <t>10363</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28793</t>
+          <t>28094</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>413489</t>
+          <t>412807</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>425703</t>
+          <t>425297</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>329671</t>
+          <t>330028</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>342202</t>
+          <t>342071</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>747354</t>
+          <t>748053</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>765556</t>
+          <t>765784</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4695</t>
+          <t>4645</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18024</t>
+          <t>18084</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10092</t>
+          <t>10658</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26725</t>
+          <t>26805</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17818</t>
+          <t>17107</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37818</t>
+          <t>37284</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>359203</t>
+          <t>359143</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>372532</t>
+          <t>372582</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>345548</t>
+          <t>345468</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>362181</t>
+          <t>361615</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>711682</t>
+          <t>712216</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>731682</t>
+          <t>732393</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,72%</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4831</t>
+          <t>4301</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17527</t>
+          <t>17493</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4068,82 +4068,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>3,35%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>4719</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1623</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>11669</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2,84%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>7,02%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>13779</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>7575</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>23104</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>3,36%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4719</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1057</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>13658</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>8,22%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>13779</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>7832</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>23756</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>504387</t>
+          <t>504421</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>517083</t>
+          <t>517613</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,82 +4181,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>96,65%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,18%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>161404</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>154454</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>164500</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>97,16%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>92,98%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>99,02%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>674257</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>664932</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>680461</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>98,0%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>96,64%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,07%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>161404</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>152465</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>165066</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,16%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>91,78%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,36%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>674257</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>664280</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>680204</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>98,0%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>96,55%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15271</t>
+          <t>15500</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35308</t>
+          <t>35817</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16819</t>
+          <t>17584</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37707</t>
+          <t>37881</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37345</t>
+          <t>37037</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66608</t>
+          <t>66109</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1114330</t>
+          <t>1113821</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1134367</t>
+          <t>1134138</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>788169</t>
+          <t>787995</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>809057</t>
+          <t>808292</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1908906</t>
+          <t>1909405</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1938169</t>
+          <t>1938477</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,13%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13961</t>
+          <t>13701</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32668</t>
+          <t>32128</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28411</t>
+          <t>28225</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>52158</t>
+          <t>54660</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>46154</t>
+          <t>46729</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>77665</t>
+          <t>78412</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>588038</t>
+          <t>588578</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>606745</t>
+          <t>607005</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>686086</t>
+          <t>683584</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>709833</t>
+          <t>710019</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1281285</t>
+          <t>1280538</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1312796</t>
+          <t>1312221</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,56%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7468</t>
+          <t>7296</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22136</t>
+          <t>21541</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31097</t>
+          <t>30371</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>58850</t>
+          <t>58505</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>42242</t>
+          <t>41657</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>72461</t>
+          <t>73797</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>265009</t>
+          <t>265604</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>279677</t>
+          <t>279849</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1023175</t>
+          <t>1023520</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1050928</t>
+          <t>1051654</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1296709</t>
+          <t>1295373</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1326928</t>
+          <t>1327513</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,96%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>68227</t>
+          <t>68218</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>106070</t>
+          <t>105187</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>113926</t>
+          <t>118189</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>161632</t>
+          <t>163273</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>194328</t>
+          <t>195314</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>255130</t>
+          <t>255319</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3279652</t>
+          <t>3280535</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3317495</t>
+          <t>3317504</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3369964</t>
+          <t>3368323</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3417670</t>
+          <t>3413407</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6662188</t>
+          <t>6661999</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6722990</t>
+          <t>6722004</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,18%</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5807,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de asma en 2023</t>
+          <t>Población con diagnóstico de asma en 2023 (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6002,12 +6002,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10111</t>
+          <t>9831</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26485</t>
+          <t>27851</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14216</t>
+          <t>13532</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28137</t>
+          <t>28322</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27567</t>
+          <t>28079</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48264</t>
+          <t>50011</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -6115,12 +6115,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>478727</t>
+          <t>477361</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>495101</t>
+          <t>495381</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>419330</t>
+          <t>419145</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>433251</t>
+          <t>433935</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>904415</t>
+          <t>902668</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>925112</t>
+          <t>924600</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,05%</t>
         </is>
       </c>
     </row>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10684</t>
+          <t>11005</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35922</t>
+          <t>37589</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16788</t>
+          <t>17127</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33237</t>
+          <t>32327</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31293</t>
+          <t>32920</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59928</t>
+          <t>60881</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -6458,12 +6458,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>416291</t>
+          <t>414624</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>441529</t>
+          <t>441208</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>348674</t>
+          <t>349584</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>365123</t>
+          <t>364784</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>774196</t>
+          <t>773243</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>802831</t>
+          <t>801204</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,05%</t>
         </is>
       </c>
     </row>
@@ -6688,12 +6688,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3270</t>
+          <t>2869</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23907</t>
+          <t>23981</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3677</t>
+          <t>3932</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11394</t>
+          <t>11053</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7176</t>
+          <t>6405</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31813</t>
+          <t>31295</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -6801,12 +6801,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>643638</t>
+          <t>643564</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>664275</t>
+          <t>664676</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6836,12 +6836,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>155517</t>
+          <t>155858</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>163234</t>
+          <t>162979</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>802643</t>
+          <t>803161</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>827280</t>
+          <t>828051</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -7031,12 +7031,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26839</t>
+          <t>25964</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51149</t>
+          <t>52850</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16435</t>
+          <t>17663</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47812</t>
+          <t>49016</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>47733</t>
+          <t>48617</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>92409</t>
+          <t>90711</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -7144,12 +7144,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>983670</t>
+          <t>981969</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1007980</t>
+          <t>1008855</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>929849</t>
+          <t>928645</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>961226</t>
+          <t>959998</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1920071</t>
+          <t>1921769</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1964747</t>
+          <t>1963863</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,58%</t>
         </is>
       </c>
     </row>
@@ -7374,12 +7374,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19230</t>
+          <t>18713</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45240</t>
+          <t>45439</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36172</t>
+          <t>36449</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>292720</t>
+          <t>297050</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>63628</t>
+          <t>64858</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>360429</t>
+          <t>405559</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>30,95%</t>
         </is>
       </c>
     </row>
@@ -7487,12 +7487,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>427487</t>
+          <t>427288</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>453497</t>
+          <t>454014</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>545126</t>
+          <t>540796</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>801674</t>
+          <t>801397</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>950144</t>
+          <t>905014</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1246945</t>
+          <t>1245715</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,05%</t>
         </is>
       </c>
     </row>
@@ -7717,12 +7717,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>537</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28157</t>
+          <t>27050</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>25070</t>
+          <t>25062</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>44344</t>
+          <t>44732</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>30973</t>
+          <t>31145</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>61738</t>
+          <t>61871</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -7830,12 +7830,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>212350</t>
+          <t>213457</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239953</t>
+          <t>239970</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>715363</t>
+          <t>714975</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>734637</t>
+          <t>734645</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>938476</t>
+          <t>938343</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>969241</t>
+          <t>969069</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,89%</t>
         </is>
       </c>
     </row>
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>94732</t>
+          <t>92206</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>155167</t>
+          <t>155587</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>148454</t>
+          <t>150125</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>489268</t>
+          <t>504164</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>268756</t>
+          <t>268324</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>623620</t>
+          <t>617581</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,89%</t>
         </is>
       </c>
     </row>
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3217856</t>
+          <t>3217436</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3278291</t>
+          <t>3280817</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3082234</t>
+          <t>3067338</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3423048</t>
+          <t>3421377</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6320906</t>
+          <t>6326945</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6675770</t>
+          <t>6676202</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,14%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1409-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1409-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>2744</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12928</t>
+          <t>13228</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13420</t>
+          <t>11909</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5987</t>
+          <t>5820</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20818</t>
+          <t>20802</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>424283</t>
+          <t>423983</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>434319</t>
+          <t>434467</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>301034</t>
+          <t>302545</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>312571</t>
+          <t>313317</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>730847</t>
+          <t>730863</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>745678</t>
+          <t>745845</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2071</t>
+          <t>2106</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14165</t>
+          <t>15648</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7129</t>
+          <t>6931</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24203</t>
+          <t>23662</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12514</t>
+          <t>12509</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32047</t>
+          <t>33071</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>404632</t>
+          <t>403149</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>416726</t>
+          <t>416691</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>313808</t>
+          <t>314349</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>330882</t>
+          <t>331080</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>724761</t>
+          <t>723737</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>744294</t>
+          <t>744299</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5571</t>
+          <t>5845</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18466</t>
+          <t>18855</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3002</t>
+          <t>2985</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15204</t>
+          <t>14905</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11021</t>
+          <t>11385</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28723</t>
+          <t>28217</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>610949</t>
+          <t>610560</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>623844</t>
+          <t>623570</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>244925</t>
+          <t>245224</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>257127</t>
+          <t>257144</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>860821</t>
+          <t>861327</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>878523</t>
+          <t>878159</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,72%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14874</t>
+          <t>14504</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35280</t>
+          <t>35286</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12635</t>
+          <t>12642</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31931</t>
+          <t>31447</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31291</t>
+          <t>33388</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>57464</t>
+          <t>59413</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1123729</t>
+          <t>1123723</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1144135</t>
+          <t>1144505</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>732791</t>
+          <t>733275</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>752087</t>
+          <t>752080</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1866267</t>
+          <t>1864318</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1892440</t>
+          <t>1890343</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,26%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5858</t>
+          <t>5394</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20373</t>
+          <t>18607</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14796</t>
+          <t>14766</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34798</t>
+          <t>34445</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24207</t>
+          <t>24564</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>47432</t>
+          <t>49860</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>490223</t>
+          <t>491989</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>504738</t>
+          <t>505202</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>725448</t>
+          <t>725801</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>745450</t>
+          <t>745480</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1223411</t>
+          <t>1220983</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1246636</t>
+          <t>1246279</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2909</t>
+          <t>2775</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13384</t>
+          <t>13344</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17569</t>
+          <t>18339</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37552</t>
+          <t>38143</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23787</t>
+          <t>24149</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>47596</t>
+          <t>47407</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>253498</t>
+          <t>253538</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>263973</t>
+          <t>264107</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1070617</t>
+          <t>1070026</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1090600</t>
+          <t>1089830</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1327455</t>
+          <t>1327644</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1351264</t>
+          <t>1350902</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,24%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>50078</t>
+          <t>49846</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>83475</t>
+          <t>82842</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>76722</t>
+          <t>77443</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>119016</t>
+          <t>115660</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>140092</t>
+          <t>138298</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>190117</t>
+          <t>188678</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3338435</t>
+          <t>3339068</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3371832</t>
+          <t>3372064</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3426716</t>
+          <t>3430072</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3469010</t>
+          <t>3468289</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6777525</t>
+          <t>6778964</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6827550</t>
+          <t>6829344</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,02%</t>
         </is>
       </c>
     </row>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3795</t>
+          <t>3335</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16285</t>
+          <t>17297</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4984</t>
+          <t>4549</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17027</t>
+          <t>16831</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10363</t>
+          <t>10733</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28094</t>
+          <t>27924</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>412807</t>
+          <t>411795</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>425297</t>
+          <t>425757</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>330028</t>
+          <t>330224</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>342071</t>
+          <t>342506</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>748053</t>
+          <t>748223</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>765784</t>
+          <t>765414</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,62%</t>
         </is>
       </c>
     </row>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4645</t>
+          <t>4575</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18084</t>
+          <t>18675</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10658</t>
+          <t>10093</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26805</t>
+          <t>26743</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17107</t>
+          <t>16728</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37284</t>
+          <t>37685</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>359143</t>
+          <t>358552</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>372582</t>
+          <t>372652</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>345468</t>
+          <t>345530</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>361615</t>
+          <t>362180</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>712216</t>
+          <t>711815</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>732393</t>
+          <t>732772</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4301</t>
+          <t>4372</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17493</t>
+          <t>17509</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11669</t>
+          <t>12442</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7575</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23104</t>
+          <t>23117</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>504421</t>
+          <t>504405</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>517613</t>
+          <t>517542</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>154454</t>
+          <t>153681</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>164500</t>
+          <t>165033</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>664932</t>
+          <t>664919</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>680461</t>
+          <t>680629</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15500</t>
+          <t>15836</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35817</t>
+          <t>34943</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17584</t>
+          <t>17660</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37881</t>
+          <t>37220</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37037</t>
+          <t>37728</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66109</t>
+          <t>64686</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1113821</t>
+          <t>1114695</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1134138</t>
+          <t>1133802</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>787995</t>
+          <t>788656</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>808292</t>
+          <t>808216</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1909405</t>
+          <t>1910828</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1938477</t>
+          <t>1937786</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,09%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13701</t>
+          <t>14097</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32128</t>
+          <t>31758</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28225</t>
+          <t>27392</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>54660</t>
+          <t>53312</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>46729</t>
+          <t>47079</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>78412</t>
+          <t>77262</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>588578</t>
+          <t>588948</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>607005</t>
+          <t>606609</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>683584</t>
+          <t>684932</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>710019</t>
+          <t>710852</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1280538</t>
+          <t>1281688</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1312221</t>
+          <t>1311871</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7296</t>
+          <t>7076</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21541</t>
+          <t>21621</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30371</t>
+          <t>30329</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>58505</t>
+          <t>57629</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>41657</t>
+          <t>41822</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>73797</t>
+          <t>73898</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>265604</t>
+          <t>265524</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>279849</t>
+          <t>280069</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1023520</t>
+          <t>1024396</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1051654</t>
+          <t>1051696</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1295373</t>
+          <t>1295272</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1327513</t>
+          <t>1327348</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,95%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>68218</t>
+          <t>69218</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>105187</t>
+          <t>104873</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>118189</t>
+          <t>114267</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>163273</t>
+          <t>163570</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>195314</t>
+          <t>193331</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>255319</t>
+          <t>256047</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3280535</t>
+          <t>3280849</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3317504</t>
+          <t>3316504</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3368323</t>
+          <t>3368026</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3413407</t>
+          <t>3417329</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6661999</t>
+          <t>6661271</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6722004</t>
+          <t>6723987</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,21%</t>
         </is>
       </c>
     </row>
@@ -5997,32 +5997,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>17274</t>
+          <t>18266</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9831</t>
+          <t>11063</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27851</t>
+          <t>30608</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6032,32 +6032,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>20161</t>
+          <t>22338</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13532</t>
+          <t>15185</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28322</t>
+          <t>30163</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6067,32 +6067,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>37435</t>
+          <t>40604</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28079</t>
+          <t>29762</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>50011</t>
+          <t>53334</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -6110,32 +6110,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>487938</t>
+          <t>532352</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>477361</t>
+          <t>520010</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>495381</t>
+          <t>539555</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6145,32 +6145,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>427306</t>
+          <t>466073</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>419145</t>
+          <t>458248</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>433935</t>
+          <t>473226</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6180,32 +6180,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>915244</t>
+          <t>998425</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>902668</t>
+          <t>985695</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>924600</t>
+          <t>1009267</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,14%</t>
         </is>
       </c>
     </row>
@@ -6223,17 +6223,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6258,17 +6258,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6293,17 +6293,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6340,32 +6340,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19505</t>
+          <t>20267</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11005</t>
+          <t>12584</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37589</t>
+          <t>32457</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6375,32 +6375,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>23749</t>
+          <t>26972</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17127</t>
+          <t>19405</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32327</t>
+          <t>36565</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6410,32 +6410,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>43253</t>
+          <t>47239</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32920</t>
+          <t>34893</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60881</t>
+          <t>62216</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -6453,32 +6453,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>432708</t>
+          <t>462945</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>414624</t>
+          <t>450755</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>441208</t>
+          <t>470628</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6488,32 +6488,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>358162</t>
+          <t>395520</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>349584</t>
+          <t>385927</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>364784</t>
+          <t>403087</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6523,32 +6523,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>790871</t>
+          <t>858465</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>773243</t>
+          <t>843488</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>801204</t>
+          <t>870811</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,15%</t>
         </is>
       </c>
     </row>
@@ -6566,17 +6566,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6601,17 +6601,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>381911</t>
+          <t>422492</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>381911</t>
+          <t>422492</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>381911</t>
+          <t>422492</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6636,17 +6636,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834124</t>
+          <t>905704</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834124</t>
+          <t>905704</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834124</t>
+          <t>905704</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6683,32 +6683,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>11886</t>
+          <t>13306</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2869</t>
+          <t>6909</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23981</t>
+          <t>23202</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6718,32 +6718,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6731</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3932</t>
+          <t>4252</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11053</t>
+          <t>12372</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6753,32 +6753,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>18618</t>
+          <t>20807</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6405</t>
+          <t>12515</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31295</t>
+          <t>30754</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -6796,32 +6796,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>655659</t>
+          <t>457437</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>643564</t>
+          <t>447541</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>664676</t>
+          <t>463834</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6831,32 +6831,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>160180</t>
+          <t>179996</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>155858</t>
+          <t>175125</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>162979</t>
+          <t>183245</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6866,32 +6866,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>815838</t>
+          <t>637434</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>803161</t>
+          <t>627487</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>828051</t>
+          <t>645726</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -6909,17 +6909,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6944,17 +6944,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6979,17 +6979,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>834456</t>
+          <t>658241</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>834456</t>
+          <t>658241</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>834456</t>
+          <t>658241</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7026,32 +7026,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>37514</t>
+          <t>42298</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25964</t>
+          <t>29822</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52850</t>
+          <t>59433</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7061,32 +7061,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>34577</t>
+          <t>39332</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17663</t>
+          <t>29901</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49016</t>
+          <t>50197</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7096,32 +7096,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>72091</t>
+          <t>81630</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>48617</t>
+          <t>65901</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>90711</t>
+          <t>100415</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -7139,32 +7139,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>997305</t>
+          <t>1089545</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>981969</t>
+          <t>1072410</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1008855</t>
+          <t>1102021</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7174,32 +7174,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>943084</t>
+          <t>821425</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>928645</t>
+          <t>810560</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>959998</t>
+          <t>830856</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7209,32 +7209,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1940389</t>
+          <t>1910970</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1921769</t>
+          <t>1892185</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1963863</t>
+          <t>1926699</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>96,69%</t>
         </is>
       </c>
     </row>
@@ -7252,17 +7252,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7287,17 +7287,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>977661</t>
+          <t>860757</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>977661</t>
+          <t>860757</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>977661</t>
+          <t>860757</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7322,17 +7322,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012480</t>
+          <t>1992600</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012480</t>
+          <t>1992600</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012480</t>
+          <t>1992600</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7369,32 +7369,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>29112</t>
+          <t>30323</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18713</t>
+          <t>19838</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45439</t>
+          <t>46141</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7404,32 +7404,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>106127</t>
+          <t>41550</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36449</t>
+          <t>32047</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>297050</t>
+          <t>51635</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7439,32 +7439,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>135239</t>
+          <t>71874</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>64858</t>
+          <t>58659</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>405559</t>
+          <t>89700</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -7482,32 +7482,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>443615</t>
+          <t>535255</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>427288</t>
+          <t>519437</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>454014</t>
+          <t>545740</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7517,32 +7517,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>731719</t>
+          <t>787353</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>540796</t>
+          <t>777268</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>801397</t>
+          <t>796856</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7552,32 +7552,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1175334</t>
+          <t>1322607</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>905014</t>
+          <t>1304781</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1245715</t>
+          <t>1335822</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,79%</t>
         </is>
       </c>
     </row>
@@ -7595,17 +7595,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>472727</t>
+          <t>565578</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>472727</t>
+          <t>565578</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>472727</t>
+          <t>565578</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7630,17 +7630,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>837846</t>
+          <t>828903</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>837846</t>
+          <t>828903</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>837846</t>
+          <t>828903</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7665,17 +7665,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1310573</t>
+          <t>1394481</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1310573</t>
+          <t>1394481</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1310573</t>
+          <t>1394481</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7697,7 +7697,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7712,32 +7712,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8777</t>
+          <t>8496</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>538</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27050</t>
+          <t>26385</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7747,32 +7747,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>33784</t>
+          <t>35735</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>25062</t>
+          <t>26463</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>44732</t>
+          <t>46910</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7782,32 +7782,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>42560</t>
+          <t>44231</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>31145</t>
+          <t>32679</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>61871</t>
+          <t>63218</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -7825,32 +7825,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>231730</t>
+          <t>228732</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>213457</t>
+          <t>210843</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239970</t>
+          <t>236690</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7860,32 +7860,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>725923</t>
+          <t>806848</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>714975</t>
+          <t>795673</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>734645</t>
+          <t>816120</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7895,32 +7895,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>957654</t>
+          <t>1035580</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>938343</t>
+          <t>1016593</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>969069</t>
+          <t>1047132</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,97%</t>
         </is>
       </c>
     </row>
@@ -7938,17 +7938,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7973,17 +7973,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>759707</t>
+          <t>842583</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>759707</t>
+          <t>842583</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>759707</t>
+          <t>842583</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8008,17 +8008,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1000214</t>
+          <t>1079811</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1000214</t>
+          <t>1079811</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1000214</t>
+          <t>1079811</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8055,32 +8055,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>124068</t>
+          <t>132956</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>92206</t>
+          <t>106542</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>155587</t>
+          <t>160450</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8090,22 +8090,22 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>225128</t>
+          <t>173427</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>150125</t>
+          <t>152427</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>504164</t>
+          <t>194990</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8125,32 +8125,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>349196</t>
+          <t>306384</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>268324</t>
+          <t>271974</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>617581</t>
+          <t>340557</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -8168,32 +8168,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3248955</t>
+          <t>3306266</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3217436</t>
+          <t>3278772</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3280817</t>
+          <t>3332680</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8203,27 +8203,27 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3346374</t>
+          <t>3457216</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3067338</t>
+          <t>3435653</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3421377</t>
+          <t>3478216</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -8238,32 +8238,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6595330</t>
+          <t>6763481</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6326945</t>
+          <t>6729308</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6676202</t>
+          <t>6797891</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,15%</t>
         </is>
       </c>
     </row>
@@ -8281,17 +8281,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3373023</t>
+          <t>3439222</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3373023</t>
+          <t>3439222</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3373023</t>
+          <t>3439222</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8316,17 +8316,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3571502</t>
+          <t>3630643</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3571502</t>
+          <t>3630643</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3571502</t>
+          <t>3630643</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8351,17 +8351,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6944526</t>
+          <t>7069865</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6944526</t>
+          <t>7069865</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6944526</t>
+          <t>7069865</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
